--- a/Manga.Manhwua/OP.xlsx
+++ b/Manga.Manhwua/OP.xlsx
@@ -79,7 +79,7 @@
     <t xml:space="preserve">Neta Chara Tensei Toka Anmarida!</t>
   </si>
   <si>
-    <t xml:space="preserve">Experience Distribution Ability - 12.1</t>
+    <t xml:space="preserve">Experience Distribution Ability</t>
   </si>
   <si>
     <t xml:space="preserve">Memoir Of The God Of War</t>
@@ -199,28 +199,32 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -479,167 +483,167 @@
   <dimension ref="A1:B20"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="116"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="116"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="4" t="n">
         <v>78</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="6" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="4" t="n">
         <v>81</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="6" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="4" t="n">
         <v>93</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="4" t="n">
         <v>69</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="4" t="n">
         <v>141</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>198</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="4" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="6" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="4" t="n">
         <v>34</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="6" t="n">
         <v>73</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="4" t="n">
         <v>312</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="6" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="4" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="5" t="n">
-        <v>0</v>
+      <c r="B19" s="6" t="n">
+        <v>12.1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B20" s="4" t="n">
         <v>234</v>
       </c>
     </row>

--- a/Manga.Manhwua/OP.xlsx
+++ b/Manga.Manhwua/OP.xlsx
@@ -572,7 +572,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>198</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
